--- a/output/yearly_total_coral_cover_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_8_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.257438594834481</v>
+        <v>1.249545343292336</v>
       </c>
       <c r="C3" t="n">
-        <v>4.584886351851205</v>
+        <v>4.692407360420316</v>
       </c>
       <c r="D3" t="n">
-        <v>6.110500888675734</v>
+        <v>6.061285876261841</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95282583536142</v>
+        <v>12.00323857997449</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.388403199462883</v>
+        <v>1.361691006968396</v>
       </c>
       <c r="C4" t="n">
-        <v>5.03415816839911</v>
+        <v>5.312497236264238</v>
       </c>
       <c r="D4" t="n">
-        <v>6.328312308994616</v>
+        <v>6.24178986559123</v>
       </c>
       <c r="E4" t="n">
-        <v>12.75087367685661</v>
+        <v>12.91597810882386</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.572237543482594</v>
+        <v>1.513634911942895</v>
       </c>
       <c r="C5" t="n">
-        <v>5.60089334628742</v>
+        <v>6.177046561133566</v>
       </c>
       <c r="D5" t="n">
-        <v>6.678807519160211</v>
+        <v>6.479435301073257</v>
       </c>
       <c r="E5" t="n">
-        <v>13.85193840893023</v>
+        <v>14.17011677414972</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.785272847501143</v>
+        <v>1.683751072045856</v>
       </c>
       <c r="C6" t="n">
-        <v>6.285379846496257</v>
+        <v>7.271411592295214</v>
       </c>
       <c r="D6" t="n">
-        <v>7.050268178829848</v>
+        <v>6.707173856181997</v>
       </c>
       <c r="E6" t="n">
-        <v>15.12092087282725</v>
+        <v>15.66233652052307</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.033192320373315</v>
+        <v>1.869899673397814</v>
       </c>
       <c r="C7" t="n">
-        <v>7.084821518367828</v>
+        <v>8.575368953700991</v>
       </c>
       <c r="D7" t="n">
-        <v>7.484833816316523</v>
+        <v>7.054473847250355</v>
       </c>
       <c r="E7" t="n">
-        <v>16.60284765505767</v>
+        <v>17.49974247434916</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.281167052868671</v>
+        <v>1.098780951007282</v>
       </c>
       <c r="C8" t="n">
-        <v>4.722204408943298</v>
+        <v>6.313125110933975</v>
       </c>
       <c r="D8" t="n">
-        <v>5.69707901497196</v>
+        <v>5.223471548335771</v>
       </c>
       <c r="E8" t="n">
-        <v>11.70045047678393</v>
+        <v>12.63537761027703</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.631271401854594</v>
+        <v>1.34927714155172</v>
       </c>
       <c r="C9" t="n">
-        <v>5.74122990376273</v>
+        <v>7.96901793248638</v>
       </c>
       <c r="D9" t="n">
-        <v>6.246907991741368</v>
+        <v>5.615510286055678</v>
       </c>
       <c r="E9" t="n">
-        <v>13.61940929735869</v>
+        <v>14.93380536009378</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.008427892371793</v>
+        <v>1.608349240096331</v>
       </c>
       <c r="C10" t="n">
-        <v>6.94259117437527</v>
+        <v>9.784818898897463</v>
       </c>
       <c r="D10" t="n">
-        <v>6.735729620383991</v>
+        <v>6.037016682555834</v>
       </c>
       <c r="E10" t="n">
-        <v>15.68674868713105</v>
+        <v>17.43018482154963</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.395021501614701</v>
+        <v>1.857791959899079</v>
       </c>
       <c r="C11" t="n">
-        <v>8.245782175832254</v>
+        <v>11.79540182094546</v>
       </c>
       <c r="D11" t="n">
-        <v>7.247178082314042</v>
+        <v>6.510500497342606</v>
       </c>
       <c r="E11" t="n">
-        <v>17.887981759761</v>
+        <v>20.16369427818715</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.816135682534603</v>
+        <v>2.098061587655386</v>
       </c>
       <c r="C12" t="n">
-        <v>9.66707558364625</v>
+        <v>13.83106812008512</v>
       </c>
       <c r="D12" t="n">
-        <v>7.867652779361447</v>
+        <v>6.956783497579536</v>
       </c>
       <c r="E12" t="n">
-        <v>20.3508640455423</v>
+        <v>22.88591320532004</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.232481744509561</v>
+        <v>2.30487421539636</v>
       </c>
       <c r="C13" t="n">
-        <v>11.14557959269861</v>
+        <v>15.85753799330919</v>
       </c>
       <c r="D13" t="n">
-        <v>8.360511606429318</v>
+        <v>7.326264750749721</v>
       </c>
       <c r="E13" t="n">
-        <v>22.73857294363749</v>
+        <v>25.48867695945527</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.864348707841735</v>
+        <v>1.32685165724365</v>
       </c>
       <c r="C14" t="n">
-        <v>7.867745736788023</v>
+        <v>10.98612987464942</v>
       </c>
       <c r="D14" t="n">
-        <v>6.354666357525796</v>
+        <v>5.610020541331634</v>
       </c>
       <c r="E14" t="n">
-        <v>16.08676080215556</v>
+        <v>17.92300207322471</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.95525854525499</v>
+        <v>1.318310452216702</v>
       </c>
       <c r="C15" t="n">
-        <v>8.5176136296142</v>
+        <v>11.96785794394215</v>
       </c>
       <c r="D15" t="n">
-        <v>6.393082145192975</v>
+        <v>5.575571014389613</v>
       </c>
       <c r="E15" t="n">
-        <v>16.86595432006217</v>
+        <v>18.86173941054846</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.302983764622168</v>
+        <v>1.488457146839717</v>
       </c>
       <c r="C16" t="n">
-        <v>10.13290276236556</v>
+        <v>14.1223327333429</v>
       </c>
       <c r="D16" t="n">
-        <v>6.902098694890861</v>
+        <v>5.941713820688461</v>
       </c>
       <c r="E16" t="n">
-        <v>19.33798522187859</v>
+        <v>21.55250370087108</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.871976887503733</v>
+        <v>1.167121305762693</v>
       </c>
       <c r="C17" t="n">
-        <v>9.442341427198356</v>
+        <v>12.89644401000399</v>
       </c>
       <c r="D17" t="n">
-        <v>6.429809326808847</v>
+        <v>5.453510322320607</v>
       </c>
       <c r="E17" t="n">
-        <v>17.74412764151094</v>
+        <v>19.51707563808729</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.159736957095516</v>
+        <v>1.295720437541983</v>
       </c>
       <c r="C18" t="n">
-        <v>11.05649173261279</v>
+        <v>15.01084385811739</v>
       </c>
       <c r="D18" t="n">
-        <v>6.898613490540785</v>
+        <v>5.753198626518988</v>
       </c>
       <c r="E18" t="n">
-        <v>20.1148421802491</v>
+        <v>22.05976292217836</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.187392789924148</v>
+        <v>1.267819167787289</v>
       </c>
       <c r="C19" t="n">
-        <v>11.85879559147737</v>
+        <v>15.99637129102555</v>
       </c>
       <c r="D19" t="n">
-        <v>7.018200178395088</v>
+        <v>5.798044861648983</v>
       </c>
       <c r="E19" t="n">
-        <v>21.0643885597966</v>
+        <v>23.06223532046183</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.44861621907014</v>
+        <v>1.376508456124453</v>
       </c>
       <c r="C20" t="n">
-        <v>13.60912412094788</v>
+        <v>18.28038769000167</v>
       </c>
       <c r="D20" t="n">
-        <v>7.440597128147278</v>
+        <v>6.098430206717379</v>
       </c>
       <c r="E20" t="n">
-        <v>23.4983374681653</v>
+        <v>25.7553263528435</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.460320257636003</v>
+        <v>0.7998494896039614</v>
       </c>
       <c r="C21" t="n">
-        <v>10.00342987512949</v>
+        <v>13.31584662925823</v>
       </c>
       <c r="D21" t="n">
-        <v>6.202564185706839</v>
+        <v>5.063206705020245</v>
       </c>
       <c r="E21" t="n">
-        <v>17.66631431847233</v>
+        <v>19.17890282388244</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_8_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.249545343292336</v>
+        <v>1.254915503234566</v>
       </c>
       <c r="C3" t="n">
-        <v>4.692407360420316</v>
+        <v>4.583845699284704</v>
       </c>
       <c r="D3" t="n">
-        <v>6.061285876261841</v>
+        <v>6.056426225125819</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00323857997449</v>
+        <v>11.89518742764509</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.361691006968396</v>
+        <v>1.379057062311817</v>
       </c>
       <c r="C4" t="n">
-        <v>5.312497236264238</v>
+        <v>5.014113719002951</v>
       </c>
       <c r="D4" t="n">
-        <v>6.24178986559123</v>
+        <v>6.252463648243379</v>
       </c>
       <c r="E4" t="n">
-        <v>12.91597810882386</v>
+        <v>12.64563442955815</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.513634911942895</v>
+        <v>1.563816229205594</v>
       </c>
       <c r="C5" t="n">
-        <v>6.177046561133566</v>
+        <v>5.562781109316313</v>
       </c>
       <c r="D5" t="n">
-        <v>6.479435301073257</v>
+        <v>6.576624039247594</v>
       </c>
       <c r="E5" t="n">
-        <v>14.17011677414972</v>
+        <v>13.7032213777695</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.683751072045856</v>
+        <v>1.782823096915794</v>
       </c>
       <c r="C6" t="n">
-        <v>7.271411592295214</v>
+        <v>6.237102106375627</v>
       </c>
       <c r="D6" t="n">
-        <v>6.707173856181997</v>
+        <v>6.871010287618595</v>
       </c>
       <c r="E6" t="n">
-        <v>15.66233652052307</v>
+        <v>14.89093549091002</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.869899673397814</v>
+        <v>2.035457573182209</v>
       </c>
       <c r="C7" t="n">
-        <v>8.575368953700991</v>
+        <v>7.05914457831776</v>
       </c>
       <c r="D7" t="n">
-        <v>7.054473847250355</v>
+        <v>7.197264904246698</v>
       </c>
       <c r="E7" t="n">
-        <v>17.49974247434916</v>
+        <v>16.29186705574667</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.098780951007282</v>
+        <v>1.277347769064921</v>
       </c>
       <c r="C8" t="n">
-        <v>6.313125110933975</v>
+        <v>4.763680054260495</v>
       </c>
       <c r="D8" t="n">
-        <v>5.223471548335771</v>
+        <v>5.442504258227308</v>
       </c>
       <c r="E8" t="n">
-        <v>12.63537761027703</v>
+        <v>11.48353208155272</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.34927714155172</v>
+        <v>1.621347836998891</v>
       </c>
       <c r="C9" t="n">
-        <v>7.96901793248638</v>
+        <v>5.848071578766044</v>
       </c>
       <c r="D9" t="n">
-        <v>5.615510286055678</v>
+        <v>5.881796459727304</v>
       </c>
       <c r="E9" t="n">
-        <v>14.93380536009378</v>
+        <v>13.35121587549224</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.608349240096331</v>
+        <v>1.998520120477615</v>
       </c>
       <c r="C10" t="n">
-        <v>9.784818898897463</v>
+        <v>7.12432670228656</v>
       </c>
       <c r="D10" t="n">
-        <v>6.037016682555834</v>
+        <v>6.301755927640404</v>
       </c>
       <c r="E10" t="n">
-        <v>17.43018482154963</v>
+        <v>15.42460275040458</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.857791959899079</v>
+        <v>2.390940050131422</v>
       </c>
       <c r="C11" t="n">
-        <v>11.79540182094546</v>
+        <v>8.513690771153925</v>
       </c>
       <c r="D11" t="n">
-        <v>6.510500497342606</v>
+        <v>6.795613900236605</v>
       </c>
       <c r="E11" t="n">
-        <v>20.16369427818715</v>
+        <v>17.70024472152195</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.098061587655386</v>
+        <v>2.814054676493075</v>
       </c>
       <c r="C12" t="n">
-        <v>13.83106812008512</v>
+        <v>10.01687779449996</v>
       </c>
       <c r="D12" t="n">
-        <v>6.956783497579536</v>
+        <v>7.27218390069193</v>
       </c>
       <c r="E12" t="n">
-        <v>22.88591320532004</v>
+        <v>20.10311637168496</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.30487421539636</v>
+        <v>3.248054052335441</v>
       </c>
       <c r="C13" t="n">
-        <v>15.85753799330919</v>
+        <v>11.55218449377424</v>
       </c>
       <c r="D13" t="n">
-        <v>7.326264750749721</v>
+        <v>7.663038773255176</v>
       </c>
       <c r="E13" t="n">
-        <v>25.48867695945527</v>
+        <v>22.46327731936486</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.32685165724365</v>
+        <v>1.884435265870625</v>
       </c>
       <c r="C14" t="n">
-        <v>10.98612987464942</v>
+        <v>8.08821681873073</v>
       </c>
       <c r="D14" t="n">
-        <v>5.610020541331634</v>
+        <v>5.852198065015236</v>
       </c>
       <c r="E14" t="n">
-        <v>17.92300207322471</v>
+        <v>15.82485014961659</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.318310452216702</v>
+        <v>1.986321042617359</v>
       </c>
       <c r="C15" t="n">
-        <v>11.96785794394215</v>
+        <v>8.758004372476075</v>
       </c>
       <c r="D15" t="n">
-        <v>5.575571014389613</v>
+        <v>5.82054651903032</v>
       </c>
       <c r="E15" t="n">
-        <v>18.86173941054846</v>
+        <v>16.56487193412375</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.488457146839717</v>
+        <v>2.372628946761437</v>
       </c>
       <c r="C16" t="n">
-        <v>14.1223327333429</v>
+        <v>10.37510973848029</v>
       </c>
       <c r="D16" t="n">
-        <v>5.941713820688461</v>
+        <v>6.218468498515636</v>
       </c>
       <c r="E16" t="n">
-        <v>21.55250370087108</v>
+        <v>18.96620718375736</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.167121305762693</v>
+        <v>1.948808462838089</v>
       </c>
       <c r="C17" t="n">
-        <v>12.89644401000399</v>
+        <v>9.626909995596755</v>
       </c>
       <c r="D17" t="n">
-        <v>5.453510322320607</v>
+        <v>5.738894562468113</v>
       </c>
       <c r="E17" t="n">
-        <v>19.51707563808729</v>
+        <v>17.31461302090296</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.295720437541983</v>
+        <v>2.270438828226386</v>
       </c>
       <c r="C18" t="n">
-        <v>15.01084385811739</v>
+        <v>11.28424738252101</v>
       </c>
       <c r="D18" t="n">
-        <v>5.753198626518988</v>
+        <v>6.136040961267074</v>
       </c>
       <c r="E18" t="n">
-        <v>22.05976292217836</v>
+        <v>19.69072717201447</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.267819167787289</v>
+        <v>2.315334150741593</v>
       </c>
       <c r="C19" t="n">
-        <v>15.99637129102555</v>
+        <v>12.11921398750588</v>
       </c>
       <c r="D19" t="n">
-        <v>5.798044861648983</v>
+        <v>6.194592394348355</v>
       </c>
       <c r="E19" t="n">
-        <v>23.06223532046183</v>
+        <v>20.62914053259582</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.376508456124453</v>
+        <v>2.619852653644868</v>
       </c>
       <c r="C20" t="n">
-        <v>18.28038769000167</v>
+        <v>13.99200572560414</v>
       </c>
       <c r="D20" t="n">
-        <v>6.098430206717379</v>
+        <v>6.547471789162828</v>
       </c>
       <c r="E20" t="n">
-        <v>25.7553263528435</v>
+        <v>23.15933016841183</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7998494896039614</v>
+        <v>1.576588638249953</v>
       </c>
       <c r="C21" t="n">
-        <v>13.31584662925823</v>
+        <v>10.33238407839147</v>
       </c>
       <c r="D21" t="n">
-        <v>5.063206705020245</v>
+        <v>5.424725479632091</v>
       </c>
       <c r="E21" t="n">
-        <v>19.17890282388244</v>
+        <v>17.33369819627351</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_8_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254915503234566</v>
+        <v>2.610820096649328</v>
       </c>
       <c r="C3" t="n">
-        <v>4.583845699284704</v>
+        <v>7.708307078974847</v>
       </c>
       <c r="D3" t="n">
-        <v>6.056426225125819</v>
+        <v>8.161315557846368</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89518742764509</v>
+        <v>18.48044273347054</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.379057062311817</v>
+        <v>1.115532504161982</v>
       </c>
       <c r="C4" t="n">
-        <v>5.014113719002951</v>
+        <v>4.485321209714025</v>
       </c>
       <c r="D4" t="n">
-        <v>6.252463648243379</v>
+        <v>5.884134453851549</v>
       </c>
       <c r="E4" t="n">
-        <v>12.64563442955815</v>
+        <v>11.48498816772756</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.563816229205594</v>
+        <v>1.246322854669702</v>
       </c>
       <c r="C5" t="n">
-        <v>5.562781109316313</v>
+        <v>5.12025093845253</v>
       </c>
       <c r="D5" t="n">
-        <v>6.576624039247594</v>
+        <v>6.296438789759494</v>
       </c>
       <c r="E5" t="n">
-        <v>13.7032213777695</v>
+        <v>12.66301258288173</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.782823096915794</v>
+        <v>1.380476166717646</v>
       </c>
       <c r="C6" t="n">
-        <v>6.237102106375627</v>
+        <v>5.934773766715728</v>
       </c>
       <c r="D6" t="n">
-        <v>6.871010287618595</v>
+        <v>6.739974756902388</v>
       </c>
       <c r="E6" t="n">
-        <v>14.89093549091002</v>
+        <v>14.05522469033576</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.035457573182209</v>
+        <v>1.518875541340799</v>
       </c>
       <c r="C7" t="n">
-        <v>7.05914457831776</v>
+        <v>6.898248525487388</v>
       </c>
       <c r="D7" t="n">
-        <v>7.197264904246698</v>
+        <v>7.327558474719248</v>
       </c>
       <c r="E7" t="n">
-        <v>16.29186705574667</v>
+        <v>15.74468254154744</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.277347769064921</v>
+        <v>1.653125494331378</v>
       </c>
       <c r="C8" t="n">
-        <v>4.763680054260495</v>
+        <v>7.97101449118281</v>
       </c>
       <c r="D8" t="n">
-        <v>5.442504258227308</v>
+        <v>7.864775901247262</v>
       </c>
       <c r="E8" t="n">
-        <v>11.48353208155272</v>
+        <v>17.48891588676145</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.621347836998891</v>
+        <v>1.785524801724513</v>
       </c>
       <c r="C9" t="n">
-        <v>5.848071578766044</v>
+        <v>9.136041046302996</v>
       </c>
       <c r="D9" t="n">
-        <v>5.881796459727304</v>
+        <v>8.423052857605878</v>
       </c>
       <c r="E9" t="n">
-        <v>13.35121587549224</v>
+        <v>19.34461870563339</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.998520120477615</v>
+        <v>1.1049374061757</v>
       </c>
       <c r="C10" t="n">
-        <v>7.12432670228656</v>
+        <v>6.705601891885861</v>
       </c>
       <c r="D10" t="n">
-        <v>6.301755927640404</v>
+        <v>6.667981319859123</v>
       </c>
       <c r="E10" t="n">
-        <v>15.42460275040458</v>
+        <v>14.47852061792068</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.390940050131422</v>
+        <v>1.039160309991164</v>
       </c>
       <c r="C11" t="n">
-        <v>8.513690771153925</v>
+        <v>7.036676670189014</v>
       </c>
       <c r="D11" t="n">
-        <v>6.795613900236605</v>
+        <v>6.637851482815789</v>
       </c>
       <c r="E11" t="n">
-        <v>17.70024472152195</v>
+        <v>14.71368846299597</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.814054676493075</v>
+        <v>1.1341345829</v>
       </c>
       <c r="C12" t="n">
-        <v>10.01687779449996</v>
+        <v>8.207616974521228</v>
       </c>
       <c r="D12" t="n">
-        <v>7.27218390069193</v>
+        <v>7.139190765466465</v>
       </c>
       <c r="E12" t="n">
-        <v>20.10311637168496</v>
+        <v>16.48094232288769</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.248054052335441</v>
+        <v>0.90103822548068</v>
       </c>
       <c r="C13" t="n">
-        <v>11.55218449377424</v>
+        <v>7.726413337284653</v>
       </c>
       <c r="D13" t="n">
-        <v>7.663038773255176</v>
+        <v>6.615899604148831</v>
       </c>
       <c r="E13" t="n">
-        <v>22.46327731936486</v>
+        <v>15.24335116691416</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.884435265870625</v>
+        <v>0.9883254138652641</v>
       </c>
       <c r="C14" t="n">
-        <v>8.08821681873073</v>
+        <v>8.957132259328453</v>
       </c>
       <c r="D14" t="n">
-        <v>5.852198065015236</v>
+        <v>7.095385182902972</v>
       </c>
       <c r="E14" t="n">
-        <v>15.82485014961659</v>
+        <v>17.04084285609669</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.986321042617359</v>
+        <v>0.9676890771219961</v>
       </c>
       <c r="C15" t="n">
-        <v>8.758004372476075</v>
+        <v>9.57592783731522</v>
       </c>
       <c r="D15" t="n">
-        <v>5.82054651903032</v>
+        <v>7.247457902290805</v>
       </c>
       <c r="E15" t="n">
-        <v>16.56487193412375</v>
+        <v>17.79107481672802</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.372628946761437</v>
+        <v>1.066600158324862</v>
       </c>
       <c r="C16" t="n">
-        <v>10.37510973848029</v>
+        <v>11.08582635401569</v>
       </c>
       <c r="D16" t="n">
-        <v>6.218468498515636</v>
+        <v>7.76900155269488</v>
       </c>
       <c r="E16" t="n">
-        <v>18.96620718375736</v>
+        <v>19.92142806503543</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.948808462838089</v>
+        <v>0.6440755813711199</v>
       </c>
       <c r="C17" t="n">
-        <v>9.626909995596755</v>
+        <v>8.269575072136242</v>
       </c>
       <c r="D17" t="n">
-        <v>5.738894562468113</v>
+        <v>6.522613937291299</v>
       </c>
       <c r="E17" t="n">
-        <v>17.31461302090296</v>
+        <v>15.43626459079866</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.270438828226386</v>
+        <v>0.5162225778470579</v>
       </c>
       <c r="C18" t="n">
-        <v>11.28424738252101</v>
+        <v>7.203740677020693</v>
       </c>
       <c r="D18" t="n">
-        <v>6.136040961267074</v>
+        <v>6.038101810291413</v>
       </c>
       <c r="E18" t="n">
-        <v>19.69072717201447</v>
+        <v>13.75806506515916</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.315334150741593</v>
+        <v>0.6109023264446203</v>
       </c>
       <c r="C19" t="n">
-        <v>12.11921398750588</v>
+        <v>8.843377152837377</v>
       </c>
       <c r="D19" t="n">
-        <v>6.194592394348355</v>
+        <v>6.71737304685978</v>
       </c>
       <c r="E19" t="n">
-        <v>20.62914053259582</v>
+        <v>16.17165252614178</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.619852653644868</v>
+        <v>0.7056998847666924</v>
       </c>
       <c r="C20" t="n">
-        <v>13.99200572560414</v>
+        <v>10.55298278753573</v>
       </c>
       <c r="D20" t="n">
-        <v>6.547471789162828</v>
+        <v>7.336973657964028</v>
       </c>
       <c r="E20" t="n">
-        <v>23.15933016841183</v>
+        <v>18.59565633026645</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.576588638249953</v>
+        <v>0.7936448441131216</v>
       </c>
       <c r="C21" t="n">
-        <v>10.33238407839147</v>
+        <v>12.33452107652425</v>
       </c>
       <c r="D21" t="n">
-        <v>5.424725479632091</v>
+        <v>7.966794262669485</v>
       </c>
       <c r="E21" t="n">
-        <v>17.33369819627351</v>
+        <v>21.09496018330685</v>
       </c>
     </row>
   </sheetData>
